--- a/data/categorias/base_2025_normalizada.xlsx
+++ b/data/categorias/base_2025_normalizada.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B382"/>
+  <dimension ref="A1:B410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DescNormalizada</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>IndCategoria</t>
         </is>
@@ -5007,6 +4995,342 @@
         </is>
       </c>
       <c r="B382" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>raia 4719</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>208 shibata</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>claudiomarianodas</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>tjmr panificadora e co</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>chiquinho sorvetes</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>globo combo</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>doacao para doare</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>gran roma comercio de</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>c mix park</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>high torque sao jose d</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>nagairo shopping ded</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>amazon br iii nupay</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>sabrinalouiseda</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>ebn playstation</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>andreaaparecida</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>valeriaalvesde</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>imigrantesctnbrp</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>mp dabruhkids</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>anagrasielysibela</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>dhs brito</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>castro carreira restau</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>mercearia e emporio da</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>b91 frios e salgados n</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>orquidea chic paes e d</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>hotdog</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>pe de salgados produto</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>crockfrango</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
         <is>
           <t>2</t>
         </is>
